--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484565_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484565_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6836</v>
+        <v>6.0936</v>
       </c>
       <c r="E2" t="n">
-        <v>9.295500000000001</v>
+        <v>6.0734</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.612</v>
+        <v>0.0202</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2722</v>
+        <v>3.9172</v>
       </c>
       <c r="H2" t="n">
-        <v>5.135</v>
+        <v>3.218</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.8628</v>
+        <v>0.6992</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1266</v>
+        <v>5.5479</v>
       </c>
       <c r="K2" t="n">
-        <v>6.3348</v>
+        <v>2.861</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7917999999999999</v>
+        <v>2.6868</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.8545</v>
+        <v>-1.6306</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1999</v>
+        <v>0.357</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.6546</v>
+        <v>-1.9876</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5656</v>
+        <v>0.5498</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1677</v>
+        <v>-0.2843</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8469</v>
+        <v>-0.4691</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3208</v>
+        <v>0.1847</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3219</v>
+        <v>1.9109</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3219</v>
+        <v>1.9109</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1643</v>
+        <v>5.2934</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4414</v>
+        <v>8.0044</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2771</v>
+        <v>-2.7111</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9172</v>
+        <v>2.2722</v>
       </c>
       <c r="H3" t="n">
-        <v>3.218</v>
+        <v>5.135</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6992</v>
+        <v>-2.8628</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5479</v>
+        <v>7.1266</v>
       </c>
       <c r="K3" t="n">
-        <v>2.861</v>
+        <v>6.3348</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6868</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6306</v>
+        <v>-4.8545</v>
       </c>
       <c r="N3" t="n">
-        <v>0.357</v>
+        <v>-1.1999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9876</v>
+        <v>-3.6546</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5498</v>
+        <v>2.5656</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2136</v>
+        <v>0.7775</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.101</v>
+        <v>0.5558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1125</v>
+        <v>0.2217</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9109</v>
+        <v>-0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9109</v>
+        <v>0.3219</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0363</v>
+        <v>4.5171</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8773</v>
+        <v>2.358</v>
       </c>
       <c r="F4" t="n">
         <v>2.159</v>
@@ -766,10 +766,10 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0369</v>
+        <v>0.5177</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4593</v>
+        <v>0.0215</v>
       </c>
       <c r="U4" t="n">
         <v>0.4962</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9243</v>
+        <v>3.8884</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9606</v>
+        <v>6.0734</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0363</v>
+        <v>-2.185</v>
       </c>
       <c r="G5" t="n">
         <v>0.5281</v>
@@ -844,13 +844,13 @@
         <v>3.2986</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.63</v>
+        <v>0.3341</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2669</v>
+        <v>-0.1542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6369</v>
+        <v>0.4883</v>
       </c>
       <c r="V5" t="n">
         <v>0.6439</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7903</v>
+        <v>0.8794</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6827</v>
+        <v>1.5804</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8924</v>
+        <v>-0.701</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0474</v>
+        <v>-0.3972</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1936</v>
+        <v>0.7439</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.241</v>
+        <v>-1.1411</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9172</v>
+        <v>1.9387</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7921</v>
+        <v>1.0279</v>
       </c>
       <c r="L8" t="n">
-        <v>0.125</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.9646</v>
+        <v>-2.3359</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5985</v>
+        <v>-0.284</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3661</v>
+        <v>-2.0519</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9318</v>
+        <v>0.6823</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5981</v>
+        <v>0.2361</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3337</v>
+        <v>0.4462</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
         <v>-0.6439</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5141</v>
+        <v>0.3251</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1407</v>
+        <v>0.3251</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6267</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3972</v>
+        <v>0.3251</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7439</v>
+        <v>0.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1411</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9387</v>
+        <v>0.3251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0279</v>
+        <v>0.3251</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9108000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3359</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.284</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0519</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2036</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5206</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3251</v>
+        <v>-0.9738</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3251</v>
+        <v>-1.0344</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3251</v>
+        <v>-0.783</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3251</v>
+        <v>0.3196</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-1.1026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3251</v>
+        <v>-1.0378</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3251</v>
+        <v>0.1609</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.1987</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.2548</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.1587</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.1599</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9331</v>
+        <v>-1.4334</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7459</v>
+        <v>0.1031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1872</v>
+        <v>-1.5365</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.783</v>
+        <v>-3.0474</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3196</v>
+        <v>0.1936</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1026</v>
+        <v>-3.241</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0378</v>
+        <v>0.9172</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1609</v>
+        <v>0.7921</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1987</v>
+        <v>0.125</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2548</v>
+        <v>-3.9646</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1587</v>
+        <v>-0.5985</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0961</v>
+        <v>-3.3661</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9163</v>
+        <v>2.3823</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2006</v>
+        <v>1.7081</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2919</v>
+        <v>1.0185</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.6896</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8576</v>
+        <v>-1.6435</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2605</v>
+        <v>-2.972</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4028</v>
+        <v>1.3285</v>
       </c>
       <c r="G12" t="n">
         <v>-2.146</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1227</v>
+        <v>0.0914</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5694</v>
+        <v>-0.2809</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4467</v>
+        <v>0.3723</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6641</v>
+        <v>-3.3668</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8756</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7886</v>
+        <v>-0.4913</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9702</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0605</v>
+        <v>0.2368</v>
       </c>
       <c r="T13" t="n">
         <v>0.2542</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3146</v>
+        <v>-0.0174</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.3134</v>
+        <v>-7.6344</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.9451</v>
+        <v>-6.4643</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3683</v>
+        <v>-1.1701</v>
       </c>
       <c r="G14" t="n">
         <v>-7.5019</v>
@@ -1546,13 +1546,13 @@
         <v>2.3823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1439</v>
+        <v>0.5351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2217</v>
+        <v>0.2591</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3011</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.145599999999996</v>
+        <v>9.4209</v>
       </c>
       <c r="E15" t="n">
-        <v>14.372</v>
+        <v>14.6473</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.226800000000001</v>
+        <v>-5.2268</v>
       </c>
       <c r="G15" t="n">
         <v>-4.472099999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>8.669700000000001</v>
+        <v>8.669699999999999</v>
       </c>
       <c r="I15" t="n">
         <v>-13.1419</v>
@@ -1609,7 +1609,7 @@
         <v>-21.6788</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.366599999999999</v>
+        <v>-4.3666</v>
       </c>
       <c r="O15" t="n">
         <v>-17.3122</v>
@@ -1624,13 +1624,13 @@
         <v>20.1583</v>
       </c>
       <c r="S15" t="n">
-        <v>4.483299999999999</v>
+        <v>4.7586</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1692</v>
+        <v>1.4444</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3143</v>
+        <v>3.3141</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9447999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.9008</v>
+        <v>10.8458</v>
       </c>
       <c r="E16" t="n">
-        <v>10.8043</v>
+        <v>10.612</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0965</v>
+        <v>0.2338</v>
       </c>
       <c r="G16" t="n">
         <v>9.421099999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4509</v>
+        <v>0.3959</v>
       </c>
       <c r="T16" t="n">
-        <v>0.126</v>
+        <v>-0.0663</v>
       </c>
       <c r="U16" t="n">
-        <v>1.325</v>
+        <v>0.4622</v>
       </c>
       <c r="V16" t="n">
         <v>1.5785</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.361</v>
+        <v>0.5431</v>
       </c>
       <c r="E18" t="n">
         <v>0.5458</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1848</v>
+        <v>-0.0028</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7652</v>
@@ -1858,13 +1858,13 @@
         <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3241</v>
+        <v>-0.142</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1589</v>
+        <v>0.0232</v>
       </c>
       <c r="V18" t="n">
         <v>1.267</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3251</v>
+        <v>0.4385</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3251</v>
+        <v>1.2947</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.8562</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3251</v>
+        <v>-1.0803</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.0803</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3251</v>
+        <v>0.0417</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.122</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.122</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0139</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2928</v>
+        <v>0.3251</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1985</v>
+        <v>0.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9056999999999999</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0803</v>
+        <v>0.3251</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0803</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0417</v>
+        <v>0.3251</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.122</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.122</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0771</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1101</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1397</v>
+        <v>0.1769</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1651</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3048</v>
+        <v>0.2681</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3626</v>
+        <v>0.7107</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3721</v>
+        <v>-0.4464</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0095</v>
+        <v>1.157</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0633</v>
+        <v>1.5262</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0217</v>
+        <v>0.6253</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0417</v>
+        <v>0.9009</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4259</v>
+        <v>-0.8155</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3938</v>
+        <v>-1.0716</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0321</v>
+        <v>0.2561</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2824</v>
+        <v>-0.5992</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2202</v>
+        <v>-0.4001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0621</v>
+        <v>-0.1991</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3219</v>
+        <v>-0.3011</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>-0.3011</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6303</v>
+        <v>0.0555</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.572</v>
+        <v>0.2612</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0583</v>
+        <v>-0.2057</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7107</v>
+        <v>-0.3626</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4464</v>
+        <v>-0.3721</v>
       </c>
       <c r="I22" t="n">
-        <v>1.157</v>
+        <v>0.0095</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5262</v>
+        <v>0.0633</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6253</v>
+        <v>0.0217</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9009</v>
+        <v>0.0417</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8155</v>
+        <v>-0.4259</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0716</v>
+        <v>-0.3938</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2561</v>
+        <v>-0.0321</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4063</v>
+        <v>-0.0871</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8808</v>
+        <v>-0.1241</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5255</v>
+        <v>0.0369</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3011</v>
+        <v>0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3011</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0068</v>
+        <v>-0.8582</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0298</v>
       </c>
       <c r="F23" t="n">
-        <v>0.023</v>
+        <v>0.1716</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0796</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5057</v>
+        <v>-0.3571</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2855</v>
+        <v>-0.1369</v>
       </c>
       <c r="V23" t="n">
         <v>0.3115</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.806</v>
+        <v>-1.6829</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4008</v>
+        <v>-1.3169</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5948</v>
+        <v>-0.366</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0168</v>
+        <v>-1.6873</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3114</v>
+        <v>-3.4084</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2946</v>
+        <v>1.7211</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9144</v>
+        <v>0.0273</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0811</v>
+        <v>-1.598</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1667</v>
+        <v>1.6253</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1024</v>
+        <v>-1.7146</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2303</v>
+        <v>-1.8104</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1279</v>
+        <v>0.0958</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3103</v>
+        <v>-0.6633</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3462</v>
+        <v>-0.428</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9641999999999999</v>
+        <v>-0.2353</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4633</v>
+        <v>-1.7887</v>
       </c>
       <c r="E25" t="n">
-        <v>3.4053</v>
+        <v>3.5014</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8686</v>
+        <v>-5.2901</v>
       </c>
       <c r="G25" t="n">
         <v>0.2438</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9949</v>
+        <v>-0.3203</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.405</v>
+        <v>-0.3088</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.59</v>
+        <v>-0.0115</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6127</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4842</v>
+        <v>-2.4106</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.99</v>
+        <v>-2.8815</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4942</v>
+        <v>0.4709</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.6873</v>
+        <v>-2.0168</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.4084</v>
+        <v>-2.3114</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7211</v>
+        <v>0.2946</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0273</v>
+        <v>-0.9144</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.598</v>
+        <v>-1.0811</v>
       </c>
       <c r="L26" t="n">
-        <v>1.6253</v>
+        <v>0.1667</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.7146</v>
+        <v>-1.1024</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.8104</v>
+        <v>-1.2303</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0958</v>
+        <v>0.1279</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3665</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4646</v>
+        <v>0.7057</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.101</v>
+        <v>-0.1346</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3635</v>
+        <v>0.8403</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.0058</v>
+        <v>-2.643</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1651</v>
+        <v>0.0689</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1708</v>
+        <v>-2.7119</v>
       </c>
       <c r="G27" t="n">
         <v>-0.9641</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.3245</v>
+        <v>-0.9617</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.405</v>
+        <v>-0.5011</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9196</v>
+        <v>-0.4606</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.7227</v>
+        <v>-3.2493</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1692</v>
+        <v>0.0231</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.5536</v>
+        <v>-3.2724</v>
       </c>
       <c r="G28" t="n">
         <v>-0.07190000000000001</v>
@@ -2638,13 +2638,13 @@
         <v>0.9163</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.8628</v>
+        <v>-0.3893</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.9359</v>
+        <v>-0.7436</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0731</v>
+        <v>0.3542</v>
       </c>
       <c r="V28" t="n">
         <v>-0.9554</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-8.016500000000001</v>
+        <v>-8.2248</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.4711</v>
+        <v>-7.3364</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.5454</v>
+        <v>-0.8883</v>
       </c>
       <c r="G29" t="n">
         <v>-0.4511</v>
@@ -2716,13 +2716,13 @@
         <v>1.6493</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.0023</v>
+        <v>-0.2106</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6569</v>
+        <v>-0.2085</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.6592</v>
+        <v>-0.0021</v>
       </c>
       <c r="V29" t="n">
         <v>-0.9658</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-9.1454</v>
+        <v>-7.222399999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>5.226500000000001</v>
+        <v>5.226499999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-14.3719</v>
+        <v>-12.449</v>
       </c>
       <c r="G30" t="n">
         <v>4.471999999999999</v>
@@ -2794,13 +2794,13 @@
         <v>10.0793</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.483499999999999</v>
+        <v>-2.5604</v>
       </c>
       <c r="T30" t="n">
-        <v>-3.3143</v>
+        <v>-3.3144</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.169</v>
+        <v>0.7539000000000002</v>
       </c>
       <c r="V30" t="n">
         <v>0.9449999999999996</v>
